--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19590-2026 artfynd.xlsx
+++ b/artfynd/A 19590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136810361</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136810443</v>
       </c>
       <c r="B3" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136811545</v>
       </c>
       <c r="B4" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
